--- a/test data/SauceDemoTestData.xlsx
+++ b/test data/SauceDemoTestData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="LoginData" sheetId="1" state="visible" r:id="rId1"/>
@@ -209,13 +209,10 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -720,7 +717,7 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col bestFit="1" customWidth="1" min="1" max="1" width="13.5546875"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="14.6640625"/>
+    <col customWidth="1" min="2" max="2" width="17.8515625"/>
     <col bestFit="1" customWidth="1" min="3" max="3" width="11.6640625"/>
     <col bestFit="1" customWidth="1" min="4" max="4" width="13.88671875"/>
     <col bestFit="1" customWidth="1" min="5" max="5" width="17.88671875"/>
@@ -1028,10 +1025,10 @@
       <c r="D2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>42</v>
       </c>
       <c r="G2" s="2">
@@ -1057,10 +1054,10 @@
       <c r="D3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>41</v>
       </c>
       <c r="G3" s="2">

--- a/test data/SauceDemoTestData.xlsx
+++ b/test data/SauceDemoTestData.xlsx
@@ -74,7 +74,7 @@
     <t>invalid_user</t>
   </si>
   <si>
-    <t xml:space="preserve">Username and password do not match</t>
+    <t xml:space="preserve">Username and password do not match any user in this service</t>
   </si>
   <si>
     <t>TC_LOGIN_004</t>
@@ -209,10 +209,13 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -721,7 +724,7 @@
     <col bestFit="1" customWidth="1" min="3" max="3" width="11.6640625"/>
     <col bestFit="1" customWidth="1" min="4" max="4" width="13.88671875"/>
     <col bestFit="1" customWidth="1" min="5" max="5" width="17.88671875"/>
-    <col bestFit="1" customWidth="1" min="6" max="6" width="7.5546875"/>
+    <col customWidth="1" min="6" max="6" width="8.7109375"/>
   </cols>
   <sheetData>
     <row r="1" ht="28.5">
@@ -784,7 +787,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" ht="42.75">
+    <row r="4" ht="57">
       <c r="A4" s="2" t="s">
         <v>16</v>
       </c>
@@ -797,7 +800,7 @@
       <c r="D4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>18</v>
       </c>
       <c r="F4" s="2" t="s">
@@ -856,7 +859,7 @@
     <col customWidth="1" min="2" max="2" width="15.421875"/>
     <col bestFit="1" customWidth="1" min="3" max="3" width="11.6640625"/>
     <col bestFit="1" customWidth="1" min="4" max="4" width="21.44140625"/>
-    <col bestFit="1" customWidth="1" min="5" max="5" width="12.77734375"/>
+    <col customWidth="1" min="5" max="5" width="19.57421875"/>
     <col bestFit="1" customWidth="1" min="6" max="6" width="7.5546875"/>
   </cols>
   <sheetData>
